--- a/verification/cases/roundtrip/with_chart/init.xlsx
+++ b/verification/cases/roundtrip/with_chart/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C69FC16D-F906-467F-92E7-F0A8BB691627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="11295" windowHeight="5580" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,8 +22,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,17 +60,37 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -98,6 +124,12 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2E68-4865-930A-7AF8D75A82D0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -132,8 +164,23 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2E68-4865-930A-7AF8D75A82D0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="49660672"/>
         <c:axId val="73939968"/>
       </c:lineChart>
@@ -142,22 +189,29 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="73939968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="73939968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="49660672"/>
         <c:crosses val="autoZero"/>
@@ -166,9 +220,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -195,7 +251,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -214,9 +276,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -254,7 +316,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -288,6 +350,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -322,9 +385,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,11 +561,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -509,7 +573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -517,7 +581,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -525,7 +589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -533,7 +597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -541,7 +605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -555,9 +619,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -565,9 +629,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
